--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261012.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261012.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>27,869</t>
+          <t>51,910</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51,910</t>
+          <t>27,869</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>44,083</t>
+          <t>26,081</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>26,081</t>
+          <t>44,083</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,839</t>
+          <t>8,121</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,121</t>
+          <t>2,839</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
